--- a/TIMES-NZ/v303/SuppXLS/Scen_LoadCurve.xlsx
+++ b/TIMES-NZ/v303/SuppXLS/Scen_LoadCurve.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AGR" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COM" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RES_TechAFs" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4120,7 +4121,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4157,7 +4158,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4194,7 +4195,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4231,7 +4232,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4268,7 +4269,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4305,7 +4306,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4342,7 +4343,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4379,7 +4380,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4416,7 +4417,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4453,7 +4454,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4490,7 +4491,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4527,7 +4528,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4564,7 +4565,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4601,7 +4602,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4638,7 +4639,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4675,7 +4676,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4712,7 +4713,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4749,7 +4750,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4786,7 +4787,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4823,7 +4824,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4860,7 +4861,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4897,7 +4898,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4934,7 +4935,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4971,7 +4972,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat*, ADCF-WH*, ADCF-PUMP*, ADCF-RFGR*, ADCF-LT*</t>
+          <t>ADCF-MoTP-Stat*, ADCF-*WH*, ADCF-PUMP*, ADCF-*RFGR*, ADCF-LT*</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -6044,7 +6045,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6081,7 +6082,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6118,7 +6119,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6155,7 +6156,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6192,7 +6193,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6229,7 +6230,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6266,7 +6267,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6303,7 +6304,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6340,7 +6341,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob,AHORT-MoTP-Mob</t>
+          <t>ALIVE-*MoTP-Mob,AHORT-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6377,7 +6378,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob,AHORT-MoTP-Mob</t>
+          <t>ALIVE-*MoTP-Mob,AHORT-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6414,7 +6415,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob,AHORT-MoTP-Mob</t>
+          <t>ALIVE-*MoTP-Mob,AHORT-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6451,7 +6452,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob,AHORT-MoTP-Mob</t>
+          <t>ALIVE-*MoTP-Mob,AHORT-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6488,7 +6489,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob,AHORT-MoTP-Mob</t>
+          <t>ALIVE-*MoTP-Mob,AHORT-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6525,7 +6526,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob,AHORT-MoTP-Mob</t>
+          <t>ALIVE-*MoTP-Mob,AHORT-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6562,7 +6563,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob,AHORT-MoTP-Mob</t>
+          <t>ALIVE-*MoTP-Mob,AHORT-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6599,7 +6600,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob,AHORT-MoTP-Mob</t>
+          <t>ALIVE-*MoTP-Mob,AHORT-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6636,7 +6637,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob,AFISH-MoTP-Mob</t>
+          <t>AFORE-*MoTP-Mob,AFISH-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6673,7 +6674,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob,AFISH-MoTP-Mob</t>
+          <t>AFORE-*MoTP-Mob,AFISH-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6710,7 +6711,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob,AFISH-MoTP-Mob</t>
+          <t>AFORE-*MoTP-Mob,AFISH-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6747,7 +6748,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob,AFISH-MoTP-Mob</t>
+          <t>AFORE-*MoTP-Mob,AFISH-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6784,7 +6785,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob,AFISH-MoTP-Mob</t>
+          <t>AFORE-*MoTP-Mob,AFISH-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6821,7 +6822,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob,AFISH-MoTP-Mob</t>
+          <t>AFORE-*MoTP-Mob,AFISH-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6858,7 +6859,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob,AFISH-MoTP-Mob</t>
+          <t>AFORE-*MoTP-Mob,AFISH-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6895,7 +6896,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob,AFISH-MoTP-Mob</t>
+          <t>AFORE-*MoTP-Mob,AFISH-*MoTP-Mob</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7005,7 +7006,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7042,7 +7043,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7079,7 +7080,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7116,7 +7117,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7153,7 +7154,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7190,7 +7191,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7227,7 +7228,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -7264,7 +7265,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -7301,7 +7302,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7338,7 +7339,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -7375,7 +7376,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -7412,7 +7413,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -7449,7 +7450,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -7486,7 +7487,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -7523,7 +7524,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -7560,7 +7561,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7597,7 +7598,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -7634,7 +7635,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -7671,7 +7672,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -7708,7 +7709,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -7745,7 +7746,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -7782,7 +7783,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -7819,7 +7820,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -7856,7 +7857,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>C_HLTH-*,-C_HLTH-SH,-C_HLTH-SC</t>
+          <t>C_HLTH-*,-C_HLTH-*SH,-C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -7893,7 +7894,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -7930,7 +7931,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -7967,7 +7968,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -8004,7 +8005,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -8041,7 +8042,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -8078,7 +8079,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -8115,7 +8116,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -8152,7 +8153,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -8189,7 +8190,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -8226,7 +8227,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -8263,7 +8264,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -8300,7 +8301,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8337,7 +8338,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8374,7 +8375,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8411,7 +8412,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8448,7 +8449,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8485,7 +8486,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -8522,7 +8523,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -8559,7 +8560,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -8596,7 +8597,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -8633,7 +8634,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8670,7 +8671,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8707,7 +8708,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8744,7 +8745,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_HLTH-*SH</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8781,7 +8782,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8818,7 +8819,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8855,7 +8856,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8892,7 +8893,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8929,7 +8930,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8966,7 +8967,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9003,7 +9004,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9040,7 +9041,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9077,7 +9078,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9114,7 +9115,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -9151,7 +9152,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9188,7 +9189,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9225,7 +9226,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9262,7 +9263,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9299,7 +9300,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9336,7 +9337,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9373,7 +9374,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9410,7 +9411,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9447,7 +9448,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9484,7 +9485,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9521,7 +9522,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9558,7 +9559,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9595,7 +9596,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9632,7 +9633,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_HLTH-*SC</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9669,7 +9670,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9706,7 +9707,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9743,7 +9744,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9780,7 +9781,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9817,7 +9818,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9854,7 +9855,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9891,7 +9892,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9928,7 +9929,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -9965,7 +9966,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10002,7 +10003,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10039,7 +10040,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10076,7 +10077,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10113,7 +10114,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10150,7 +10151,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10187,7 +10188,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -10224,7 +10225,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -10261,7 +10262,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -10298,7 +10299,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -10335,7 +10336,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -10372,7 +10373,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -10409,7 +10410,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -10446,7 +10447,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -10483,7 +10484,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -10520,7 +10521,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>C_OTH-*,-C_OTH-SH,-C_OTH-SC</t>
+          <t>C_OTH-*,-C_OTH-*SH,-C_OTH-*SC</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -10557,7 +10558,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -10594,7 +10595,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -10631,7 +10632,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -10668,7 +10669,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -10705,7 +10706,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -10742,7 +10743,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -10779,7 +10780,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -10816,7 +10817,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -10853,7 +10854,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -10890,7 +10891,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -10927,7 +10928,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -10964,7 +10965,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -11001,7 +11002,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -11038,7 +11039,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -11075,7 +11076,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -11112,7 +11113,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -11149,7 +11150,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -11186,7 +11187,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -11223,7 +11224,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -11260,7 +11261,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -11297,7 +11298,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -11334,7 +11335,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -11371,7 +11372,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -11408,7 +11409,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_OTH-*SH</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -11445,7 +11446,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11482,7 +11483,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11519,7 +11520,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11556,7 +11557,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11593,7 +11594,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11630,7 +11631,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11667,7 +11668,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11704,7 +11705,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11741,7 +11742,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11778,7 +11779,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11815,7 +11816,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11852,7 +11853,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11889,7 +11890,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -11926,7 +11927,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -11963,7 +11964,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12000,7 +12001,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12037,7 +12038,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12074,7 +12075,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12111,7 +12112,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12148,7 +12149,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12185,7 +12186,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12222,7 +12223,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12259,7 +12260,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12296,7 +12297,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_OTH-*SC</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -13221,7 +13222,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -13258,7 +13259,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -13295,7 +13296,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -13332,7 +13333,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -13369,7 +13370,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -13406,7 +13407,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -13443,7 +13444,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -13480,7 +13481,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -13517,7 +13518,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -13554,7 +13555,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -13591,7 +13592,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -13628,7 +13629,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -13665,7 +13666,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -13702,7 +13703,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -13739,7 +13740,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -13776,7 +13777,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -13813,7 +13814,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -13850,7 +13851,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -13887,7 +13888,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -13924,7 +13925,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -13961,7 +13962,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -13998,7 +13999,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -14035,7 +14036,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -14072,7 +14073,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>C_OFFC*</t>
+          <t>C_OFFC*, C_DATA*</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -31044,4 +31045,1693 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Residential_AF_Slice</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Forces space heating demand devices to match COM_FR, meaning the model can no longer swap heating techs during high-cost slices</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>~TFM_INS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TimeSlice</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pset_PN</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AllRegions</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>LimType</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FAL-WK-D</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FAL-WK-N</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FAL-WK-P</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FAL-WE-D</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FAL-WE-N</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FAL-WE-P</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SPR-WK-D</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SPR-WK-N</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SPR-WK-P</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SPR-WE-D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SPR-WE-N</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SPR-WE-P</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SUM-WK-D</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SUM-WK-N</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SUM-WK-P</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SUM-WE-D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SUM-WE-N</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SUM-WE-P</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WIN-WK-D</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WIN-WK-N</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>WIN-WK-P</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WIN-WE-D</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>WIN-WE-N</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>WIN-WE-P</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FAL-WK-D</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FAL-WK-N</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FAL-WK-P</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FAL-WE-D</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FAL-WE-N</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FAL-WE-P</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SPR-WK-D</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SPR-WK-N</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SPR-WK-P</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SPR-WE-D</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SPR-WE-N</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SPR-WE-P</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SUM-WK-D</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SUM-WK-N</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SUM-WK-P</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SUM-WE-D</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SUM-WE-N</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SUM-WE-P</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>WIN-WK-D</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>WIN-WK-N</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>WIN-WK-P</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>WIN-WE-D</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>WIN-WE-N</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NCAP_AF</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>WIN-WE-P</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>Residential_Reset_AFA_for_TS_AF</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>Resets AFA to default after baseyear for techs where we have added slice AFs, to ensure no clashes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>~TFM_INS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pset_PN</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AllRegions</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NCAP_AFA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NCAP_AFA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RES*ELC*S_HEAT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>